--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0010_ses-01_WMprob_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0010_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -955,7 +956,7 @@
         <v>0.036774496252805711</v>
       </c>
       <c r="D24" s="0">
-        <v>0.045680763590027255</v>
+        <v>0.045680763590027256</v>
       </c>
       <c r="E24" s="0">
         <v>0.27208448939407553</v>
@@ -1075,7 +1076,7 @@
         <v>1.543602136101911</v>
       </c>
       <c r="F27" s="0">
-        <v>1.3080813593858009</v>
+        <v>1.308081359385801</v>
       </c>
       <c r="G27" s="0">
         <v>1.5489841078253859</v>
@@ -1212,7 +1213,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>3.5886580683272586</v>
+        <v>3.5886580683272587</v>
       </c>
       <c r="B31" s="0">
         <v>7.1052631578947301</v>
@@ -1318,7 +1319,7 @@
         <v>4.913507545086488</v>
       </c>
       <c r="K33" s="0">
-        <v>6.8298969072164883</v>
+        <v>6.8298969072164884</v>
       </c>
       <c r="L33" s="0">
         <v>4.2935340403694795</v>
@@ -1332,7 +1333,7 @@
         <v>4.122807017543856</v>
       </c>
       <c r="C34" s="0">
-        <v>4.620905667076677</v>
+        <v>4.6209056670766771</v>
       </c>
       <c r="D34" s="0">
         <v>5.8327122352318845</v>
@@ -1432,7 +1433,7 @@
         <v>2.8340080971659893</v>
       </c>
       <c r="K36" s="0">
-        <v>1.9329896907216479</v>
+        <v>1.932989690721648</v>
       </c>
       <c r="L36" s="0">
         <v>3.8223493919696416</v>
@@ -1502,7 +1503,7 @@
         <v>2.3745952394478196</v>
       </c>
       <c r="I38" s="0">
-        <v>3.4696431054000882</v>
+        <v>3.4696431054000883</v>
       </c>
       <c r="J38" s="0">
         <v>2.2451232977548745</v>
@@ -1540,7 +1541,7 @@
         <v>2.6813611316252888</v>
       </c>
       <c r="I39" s="0">
-        <v>3.3643820380925868</v>
+        <v>3.3643820380925869</v>
       </c>
       <c r="J39" s="0">
         <v>2.0979020979020961</v>
@@ -1645,7 +1646,7 @@
         <v>2.8962677884185064</v>
       </c>
       <c r="F42" s="0">
-        <v>2.7799003020048731</v>
+        <v>2.7799003020048732</v>
       </c>
       <c r="G42" s="0">
         <v>3.2589016294508117</v>
@@ -1701,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="L43" s="0">
-        <v>2.6327247846235164</v>
+        <v>2.6327247846235165</v>
       </c>
     </row>
     <row r="44">
@@ -1724,7 +1725,7 @@
         <v>2.5415711530764447</v>
       </c>
       <c r="G44" s="0">
-        <v>2.2530677932005609</v>
+        <v>2.253067793200561</v>
       </c>
       <c r="H44" s="0">
         <v>2.4427654377094794</v>
@@ -1885,7 +1886,7 @@
         <v>1.9364064268832777</v>
       </c>
       <c r="J48" s="0">
-        <v>1.7666543982333442</v>
+        <v>1.7666543982333443</v>
       </c>
       <c r="K48" s="0">
         <v>0.12886597938144317</v>
@@ -1908,7 +1909,7 @@
         <v>1.8656985550453185</v>
       </c>
       <c r="E49" s="0">
-        <v>2.2106864763268574</v>
+        <v>2.2106864763268575</v>
       </c>
       <c r="F49" s="0">
         <v>1.9721282247207348</v>
@@ -1934,7 +1935,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>2.0773850546421166</v>
+        <v>2.0773850546421167</v>
       </c>
       <c r="B50" s="0">
         <v>2.5438596491228047</v>
@@ -1952,10 +1953,10 @@
         <v>1.9412000145544501</v>
       </c>
       <c r="G50" s="0">
-        <v>2.2530677932005609</v>
+        <v>2.253067793200561</v>
       </c>
       <c r="H50" s="0">
-        <v>1.9882974492984133</v>
+        <v>1.9882974492984134</v>
       </c>
       <c r="I50" s="0">
         <v>1.6504140930666706</v>
@@ -1984,7 +1985,7 @@
         <v>1.7502945207126186</v>
       </c>
       <c r="E51" s="0">
-        <v>2.0501804946448265</v>
+        <v>2.0501804946448266</v>
       </c>
       <c r="F51" s="0">
         <v>1.8757049812611415</v>
@@ -2051,7 +2052,7 @@
         <v>1.9321650093531537</v>
       </c>
       <c r="B53" s="0">
-        <v>2.1052631578947349</v>
+        <v>2.105263157894735</v>
       </c>
       <c r="C53" s="0">
         <v>1.7639077340569862</v>
@@ -2282,7 +2283,7 @@
         <v>0.087719298245613961</v>
       </c>
       <c r="C59" s="0">
-        <v>1.1856604826335599</v>
+        <v>1.18566048263356</v>
       </c>
       <c r="D59" s="0">
         <v>0.8775515110715737</v>
@@ -2367,7 +2368,7 @@
         <v>1.173662698767862</v>
       </c>
       <c r="F61" s="0">
-        <v>1.1134155659862452</v>
+        <v>1.1134155659862453</v>
       </c>
       <c r="G61" s="0">
         <v>1.1868839267752955</v>
@@ -2385,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="L61" s="0">
-        <v>1.0823251329580434</v>
+        <v>1.0823251329580435</v>
       </c>
     </row>
     <row r="62">
@@ -2461,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="0">
-        <v>0.96569526949273687</v>
+        <v>0.96569526949273688</v>
       </c>
     </row>
     <row r="64">
@@ -2560,7 +2561,7 @@
         <v>0.85689335225412</v>
       </c>
       <c r="G66" s="0">
-        <v>0.6638503319251654</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H66" s="0">
         <v>0.75555303073339708</v>
@@ -2753,7 +2754,7 @@
         <v>0.62361697847515529</v>
       </c>
       <c r="H71" s="0">
-        <v>0.67602113276146047</v>
+        <v>0.67602113276146048</v>
       </c>
       <c r="I71" s="0">
         <v>0.39522551687156127</v>
@@ -2770,7 +2771,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.53411440385940689</v>
+        <v>0.5341144038594069</v>
       </c>
       <c r="B72" s="0">
         <v>0.87719298245613953</v>
@@ -2779,7 +2780,7 @@
         <v>0.45777907404354573</v>
       </c>
       <c r="D72" s="0">
-        <v>0.28610583511648568</v>
+        <v>0.28610583511648569</v>
       </c>
       <c r="E72" s="0">
         <v>0.40514335153196662</v>
@@ -2879,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="L74" s="0">
-        <v>0.45718906478400106</v>
+        <v>0.45718906478400107</v>
       </c>
     </row>
     <row r="75">
@@ -3004,7 +3005,7 @@
         <v>0.087719298245613961</v>
       </c>
       <c r="C78" s="0">
-        <v>0.1610469318657349</v>
+        <v>0.16104693186573491</v>
       </c>
       <c r="D78" s="0">
         <v>0.13704229077008137</v>
@@ -3150,7 +3151,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.18706310918578511</v>
+        <v>0.18706310918578512</v>
       </c>
       <c r="B82" s="0">
         <v>0.087719298245614932</v>
@@ -3171,7 +3172,7 @@
         <v>0.20116676725005234</v>
       </c>
       <c r="H82" s="0">
-        <v>0.14770209623359803</v>
+        <v>0.14770209623359804</v>
       </c>
       <c r="I82" s="0">
         <v>0.037735099600802749</v>
@@ -3247,7 +3248,7 @@
         <v>0.12070006035003007</v>
       </c>
       <c r="H84" s="0">
-        <v>0.090893597682213167</v>
+        <v>0.090893597682213168</v>
       </c>
       <c r="I84" s="0">
         <v>0.047665388969434529</v>
@@ -3530,7 +3531,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B92" s="0">
         <v>0.087719298245613961</v>
@@ -3644,7 +3645,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B95" s="0">
         <v>0</v>
